--- a/appointment_forms/014_massage_therapy_billing_form--appointment_forms.xlsx
+++ b/appointment_forms/014_massage_therapy_billing_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'massage'}</t>
+          <t>massage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Massage'}</t>
+          <t>Massage</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'physical_therapy'}</t>
+          <t>physical_therapy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Therapy'}</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'insurance'}</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Insurance'}</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'in-office'}</t>
+          <t>in-office</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'In-Office'}</t>
+          <t>In-Office</t>
         </is>
       </c>
     </row>
